--- a/asset/template.xlsx
+++ b/asset/template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Downloads\Bunis\Skripsi\Hard Cover\Manual Result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Downloads\Bunis\Skripsi\App\skripsi-kraepelin-paper-evaluation\digit-recognition-engine\asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8F9C5C3-002A-4B5B-B193-0155C7AD9A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C18FBB3-4BCB-4B66-AA7B-268D9C233A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{C4F1E2F8-9DB5-4B79-969B-9BBBDD7E1CD2}"/>
+    <workbookView xWindow="3465" yWindow="3465" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{C4F1E2F8-9DB5-4B79-969B-9BBBDD7E1CD2}"/>
   </bookViews>
   <sheets>
     <sheet name="Question" sheetId="1" r:id="rId1"/>
@@ -680,13 +680,129 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="85">
+  <dxfs count="79">
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -953,164 +1069,6 @@
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2244,7 +2202,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{ADC3901E-66A4-4D6D-A7A6-62B28D7E0A32}" name="Table1" displayName="Table1" ref="A1:FE57" totalsRowShown="0" headerRowDxfId="84">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{ADC3901E-66A4-4D6D-A7A6-62B28D7E0A32}" name="Table1" displayName="Table1" ref="A1:FE57" totalsRowShown="0" headerRowDxfId="40">
   <autoFilter ref="A1:FE57" xr:uid="{ADC3901E-66A4-4D6D-A7A6-62B28D7E0A32}"/>
   <tableColumns count="161">
     <tableColumn id="1" xr3:uid="{A161A549-7EA6-47D5-9CF5-D8D385912AB2}" name="Number"/>
@@ -2255,7 +2213,7 @@
     <tableColumn id="4" xr3:uid="{56570DB5-8DED-4288-92B7-ACC746DE56FB}" name="Answer 1">
       <calculatedColumnFormula>MOD(B2+B1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{2ED95FDB-1A8F-43FD-ABD9-2C03A5106076}" name="Label 1" dataDxfId="83">
+    <tableColumn id="5" xr3:uid="{2ED95FDB-1A8F-43FD-ABD9-2C03A5106076}" name="Label 1" dataDxfId="39">
       <calculatedColumnFormula>IF(C2=D2,TRUE,IF(D2="SKIPPED","SKIPPED",IF(D2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{E88FEEAA-63E7-410F-B0CB-D11B4740DB87}" name="Soal 2"/>
@@ -2265,7 +2223,7 @@
     <tableColumn id="8" xr3:uid="{CC7D9FC4-D8F6-4BE8-93A1-4794DD120A00}" name="Answer 2">
       <calculatedColumnFormula>MOD(F2+F1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{D568AB81-745C-4706-A4FE-DD31BD11DF49}" name="Label 2" dataDxfId="82">
+    <tableColumn id="9" xr3:uid="{D568AB81-745C-4706-A4FE-DD31BD11DF49}" name="Label 2" dataDxfId="38">
       <calculatedColumnFormula>IF(G2=H2,TRUE,IF(H2="SKIPPED","SKIPPED",IF(H2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{5E1345E4-D8CD-48BD-A2E4-62C5A15F30FA}" name="Soal 3"/>
@@ -2275,7 +2233,7 @@
     <tableColumn id="12" xr3:uid="{E24C404C-40AF-4C68-913F-E2F7B3B12FD3}" name="Answer 3">
       <calculatedColumnFormula>MOD(J2+J1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{BE5B496A-F49E-4526-ABF3-2FF666769246}" name="Label 3" dataDxfId="81">
+    <tableColumn id="13" xr3:uid="{BE5B496A-F49E-4526-ABF3-2FF666769246}" name="Label 3" dataDxfId="37">
       <calculatedColumnFormula>IF(K2=L2,TRUE,IF(L2="SKIPPED","SKIPPED",IF(L2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{F7E81FF5-0253-4284-AAD4-5AB370EC4700}" name="Soal 4"/>
@@ -2285,7 +2243,7 @@
     <tableColumn id="16" xr3:uid="{E9C8D2C1-334A-4E79-8252-AED965CB136F}" name="Answer 4">
       <calculatedColumnFormula>MOD(N2+N1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{589C7364-14D8-44BD-B02D-05CB5AA5D294}" name="Label 4" dataDxfId="80">
+    <tableColumn id="17" xr3:uid="{589C7364-14D8-44BD-B02D-05CB5AA5D294}" name="Label 4" dataDxfId="36">
       <calculatedColumnFormula>IF(O2=P2,TRUE,IF(P2="SKIPPED","SKIPPED",IF(P2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="18" xr3:uid="{44D955E0-6CC7-4CA6-B1E3-87FCA2D258D1}" name="Soal 5"/>
@@ -2295,7 +2253,7 @@
     <tableColumn id="20" xr3:uid="{F626A971-15C8-4C25-B9FE-443110B7D9BF}" name="Answer 5">
       <calculatedColumnFormula>MOD(R2+R1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{251C627A-FB58-4CC3-BC8F-89425403C84D}" name="Label 5" dataDxfId="79">
+    <tableColumn id="21" xr3:uid="{251C627A-FB58-4CC3-BC8F-89425403C84D}" name="Label 5" dataDxfId="35">
       <calculatedColumnFormula>IF(S2=T2,TRUE,IF(T2="SKIPPED","SKIPPED",IF(T2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="22" xr3:uid="{DBDCFA61-983B-49A1-BBA0-EF007DD016E1}" name="Soal 6"/>
@@ -2305,7 +2263,7 @@
     <tableColumn id="24" xr3:uid="{12E0A0E1-EEF9-4D85-9A09-A9109AB67DF7}" name="Answer 6">
       <calculatedColumnFormula>MOD(V2+V1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{63049EC5-C419-4F4E-A359-E6BF13E8E95D}" name="Label 6" dataDxfId="78">
+    <tableColumn id="25" xr3:uid="{63049EC5-C419-4F4E-A359-E6BF13E8E95D}" name="Label 6" dataDxfId="34">
       <calculatedColumnFormula>IF(W2=X2,TRUE,IF(X2="SKIPPED","SKIPPED",IF(X2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="26" xr3:uid="{88661FB9-8D3B-4ED7-AFC4-970F04E30A7F}" name="Soal 7"/>
@@ -2315,7 +2273,7 @@
     <tableColumn id="28" xr3:uid="{B53D8D06-B3B7-4DCA-9F48-3C769EDD3D83}" name="Answer 7">
       <calculatedColumnFormula>MOD(Z2+Z1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{DD1486C5-61B9-440F-9B1D-03A79D65D931}" name="Label 7" dataDxfId="77">
+    <tableColumn id="29" xr3:uid="{DD1486C5-61B9-440F-9B1D-03A79D65D931}" name="Label 7" dataDxfId="33">
       <calculatedColumnFormula>IF(AA2=AB2,TRUE,IF(AB2="SKIPPED","SKIPPED",IF(AB2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="30" xr3:uid="{1C85189C-7BAE-4EE2-9C77-26EAD3AB3E70}" name="Soal 8"/>
@@ -2325,7 +2283,7 @@
     <tableColumn id="32" xr3:uid="{A9898AF0-A30D-4012-8F3D-B1AC4CCF59F6}" name="Answer 8">
       <calculatedColumnFormula>MOD(AD2+AD1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{EA33E458-B861-4327-B75B-5BCC564BD473}" name="Label 8" dataDxfId="76">
+    <tableColumn id="33" xr3:uid="{EA33E458-B861-4327-B75B-5BCC564BD473}" name="Label 8" dataDxfId="32">
       <calculatedColumnFormula>IF(AE2=AF2,TRUE,IF(AF2="SKIPPED","SKIPPED",IF(AF2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="34" xr3:uid="{1F4B82D7-F087-4CDA-B383-C08EB39976BD}" name="Soal 9"/>
@@ -2335,7 +2293,7 @@
     <tableColumn id="36" xr3:uid="{E2954A8F-4535-4700-9D90-B55E20BE4AF4}" name="Answer 9">
       <calculatedColumnFormula>MOD(AH2+AH1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{F2A874CB-BA27-470E-9310-BD653229443E}" name="Label 9" dataDxfId="75">
+    <tableColumn id="37" xr3:uid="{F2A874CB-BA27-470E-9310-BD653229443E}" name="Label 9" dataDxfId="31">
       <calculatedColumnFormula>IF(AI2=AJ2,TRUE,IF(AJ2="SKIPPED","SKIPPED",IF(AJ2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="38" xr3:uid="{D844E2F7-4678-4B8E-BEA4-1EC2C0DC40FD}" name="Soal 10"/>
@@ -2345,7 +2303,7 @@
     <tableColumn id="40" xr3:uid="{361BAE09-C2E6-483F-8440-8D58CB9DA883}" name="Answer 10">
       <calculatedColumnFormula>MOD(AL2+AL1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="41" xr3:uid="{1014C847-608A-4555-ABEE-56FF71089A85}" name="Label 10" dataDxfId="74">
+    <tableColumn id="41" xr3:uid="{1014C847-608A-4555-ABEE-56FF71089A85}" name="Label 10" dataDxfId="30">
       <calculatedColumnFormula>IF(AM2=AN2,TRUE,IF(AN2="SKIPPED","SKIPPED",IF(AN2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="42" xr3:uid="{1D9D32D9-D355-438D-B62B-C8E0799E95FC}" name="Soal 11"/>
@@ -2355,7 +2313,7 @@
     <tableColumn id="44" xr3:uid="{D705D6B3-EF36-40D7-ABD0-04276947C384}" name="Answer 11">
       <calculatedColumnFormula>MOD(AP2+AP1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="45" xr3:uid="{42E9F24E-BC0F-432E-8DAD-60547AE06681}" name="Label 11" dataDxfId="73">
+    <tableColumn id="45" xr3:uid="{42E9F24E-BC0F-432E-8DAD-60547AE06681}" name="Label 11" dataDxfId="29">
       <calculatedColumnFormula>IF(AQ2=AR2,TRUE,IF(AR2="SKIPPED","SKIPPED",IF(AR2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="46" xr3:uid="{75C705E0-84DA-42CB-B589-9D3E88A993F7}" name="Soal 12"/>
@@ -2365,7 +2323,7 @@
     <tableColumn id="48" xr3:uid="{84DE9BB5-9FA7-41BD-B8A4-23A298D61341}" name="Answer 12">
       <calculatedColumnFormula>MOD(AT2+AT1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="49" xr3:uid="{3DD408FF-A67D-4115-BAC1-2D503E80235A}" name="Label 12" dataDxfId="72">
+    <tableColumn id="49" xr3:uid="{3DD408FF-A67D-4115-BAC1-2D503E80235A}" name="Label 12" dataDxfId="28">
       <calculatedColumnFormula>IF(AU2=AV2,TRUE,IF(AV2="SKIPPED","SKIPPED",IF(AV2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="50" xr3:uid="{F4D6E2BE-97D3-49CD-AFD1-872DD12DC938}" name="Soal 13"/>
@@ -2375,7 +2333,7 @@
     <tableColumn id="52" xr3:uid="{0EB3385F-B61E-47BB-8CD9-4FEDDE305D36}" name="Answer 13">
       <calculatedColumnFormula>MOD(AX2+AX1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="53" xr3:uid="{AC1B05E6-7D5A-4FCC-8CCD-487C200C738E}" name="Label 13" dataDxfId="71">
+    <tableColumn id="53" xr3:uid="{AC1B05E6-7D5A-4FCC-8CCD-487C200C738E}" name="Label 13" dataDxfId="27">
       <calculatedColumnFormula>IF(AY2=AZ2,TRUE,IF(AZ2="SKIPPED","SKIPPED",IF(AZ2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="54" xr3:uid="{AF654337-4CED-4FFF-BC92-070F17B1705E}" name="Soal 14"/>
@@ -2385,7 +2343,7 @@
     <tableColumn id="56" xr3:uid="{160029D6-76AD-4DAB-AAEC-0FEBDADD6D18}" name="Answer 14">
       <calculatedColumnFormula>MOD(BB2+BB1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="57" xr3:uid="{38E86538-66BA-4414-84FE-4D5B0DD797DD}" name="Label 14" dataDxfId="70">
+    <tableColumn id="57" xr3:uid="{38E86538-66BA-4414-84FE-4D5B0DD797DD}" name="Label 14" dataDxfId="26">
       <calculatedColumnFormula>IF(BC2=BD2,TRUE,IF(BD2="SKIPPED","SKIPPED",IF(BD2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="58" xr3:uid="{53DB3962-7A64-4C48-96AC-C9AE3ECC68B0}" name="Soal 15"/>
@@ -2395,7 +2353,7 @@
     <tableColumn id="60" xr3:uid="{A9B8EDE6-15CE-4AFB-9C11-5DD29A127A3B}" name="Answer 15">
       <calculatedColumnFormula>MOD(BF2+BF1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="61" xr3:uid="{57ED98D6-E149-494E-9ECB-3045847A6838}" name="Label 15" dataDxfId="69">
+    <tableColumn id="61" xr3:uid="{57ED98D6-E149-494E-9ECB-3045847A6838}" name="Label 15" dataDxfId="25">
       <calculatedColumnFormula>IF(BG2=BH2,TRUE,IF(BH2="SKIPPED","SKIPPED",IF(BH2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="62" xr3:uid="{1B1A2B6D-7373-4940-9A50-A3315BC24E84}" name="Soal 16"/>
@@ -2405,7 +2363,7 @@
     <tableColumn id="64" xr3:uid="{23F80BC8-8804-4BFC-A350-FBF0E0C34717}" name="Answer 16">
       <calculatedColumnFormula>MOD(BJ2+BJ1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="65" xr3:uid="{70ACE694-A24C-494F-838C-2DE0F4E0D7BC}" name="Label 16" dataDxfId="68">
+    <tableColumn id="65" xr3:uid="{70ACE694-A24C-494F-838C-2DE0F4E0D7BC}" name="Label 16" dataDxfId="24">
       <calculatedColumnFormula>IF(BK2=BL2,TRUE,IF(BL2="SKIPPED","SKIPPED",IF(BL2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="66" xr3:uid="{612FD0D5-FD18-4C9C-973F-473086B4B4FC}" name="Soal 17"/>
@@ -2415,7 +2373,7 @@
     <tableColumn id="68" xr3:uid="{F187B09E-C4FD-4C78-832D-8ADE2DB31EAF}" name="Answer 17">
       <calculatedColumnFormula>MOD(BN2+BN1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="69" xr3:uid="{303A8929-DA24-4249-9BD1-29AB13908B60}" name="Label 17" dataDxfId="67">
+    <tableColumn id="69" xr3:uid="{303A8929-DA24-4249-9BD1-29AB13908B60}" name="Label 17" dataDxfId="23">
       <calculatedColumnFormula>IF(BO2=BP2,TRUE,IF(BP2="SKIPPED","SKIPPED",IF(BP2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="70" xr3:uid="{9FE5C4C3-E044-4DEF-8EA0-17E45349F048}" name="Soal 18"/>
@@ -2425,7 +2383,7 @@
     <tableColumn id="72" xr3:uid="{08588C38-DE85-4AC0-9D6D-1408F0AB117D}" name="Answer 18">
       <calculatedColumnFormula>MOD(BR2+BR1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="73" xr3:uid="{85144663-355E-4726-9480-F196A9B4E3EA}" name="Label 18" dataDxfId="66">
+    <tableColumn id="73" xr3:uid="{85144663-355E-4726-9480-F196A9B4E3EA}" name="Label 18" dataDxfId="22">
       <calculatedColumnFormula>IF(BS2=BT2,TRUE,IF(BT2="SKIPPED","SKIPPED",IF(BT2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="74" xr3:uid="{512F4677-B7BB-434A-BEA6-89EECDD027FE}" name="Soal 19"/>
@@ -2435,7 +2393,7 @@
     <tableColumn id="76" xr3:uid="{E070C738-0C33-4E97-8311-91D75E91BC95}" name="Answer 19">
       <calculatedColumnFormula>MOD(BV2+BV1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="77" xr3:uid="{B43876B4-95AC-4083-821B-B830CC4B557B}" name="Label 19" dataDxfId="65">
+    <tableColumn id="77" xr3:uid="{B43876B4-95AC-4083-821B-B830CC4B557B}" name="Label 19" dataDxfId="21">
       <calculatedColumnFormula>IF(BW2=BX2,TRUE,IF(BX2="SKIPPED","SKIPPED",IF(BX2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="78" xr3:uid="{3C70BBDC-C4C3-4916-89FE-4BF9DFE90FCA}" name="Soal 20"/>
@@ -2445,7 +2403,7 @@
     <tableColumn id="80" xr3:uid="{D3D6F631-4F41-431B-8271-2C21BF70494E}" name="Answer 20">
       <calculatedColumnFormula>MOD(BZ2+BZ1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="81" xr3:uid="{788C3CDD-38D3-4436-8388-79118CD339F3}" name="Label 20" dataDxfId="64">
+    <tableColumn id="81" xr3:uid="{788C3CDD-38D3-4436-8388-79118CD339F3}" name="Label 20" dataDxfId="20">
       <calculatedColumnFormula>IF(CA2=CB2,TRUE,IF(CB2="SKIPPED","SKIPPED",IF(CB2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="82" xr3:uid="{601788DD-6209-4DE2-B8B9-82287EDC646F}" name="Soal 21"/>
@@ -2455,7 +2413,7 @@
     <tableColumn id="84" xr3:uid="{6DC0E09E-0F89-476E-901E-0CE81E65FED6}" name="Answer 21">
       <calculatedColumnFormula>MOD(CD2+CD1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="85" xr3:uid="{53062F47-8ACB-4F14-AD0A-E8CE5F58930E}" name="Label 21" dataDxfId="63">
+    <tableColumn id="85" xr3:uid="{53062F47-8ACB-4F14-AD0A-E8CE5F58930E}" name="Label 21" dataDxfId="19">
       <calculatedColumnFormula>IF(CE2=CF2,TRUE,IF(CF2="SKIPPED","SKIPPED",IF(CF2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="86" xr3:uid="{868AC094-7FB8-45FC-B9BC-697480CA6BFB}" name="Soal 22"/>
@@ -2465,7 +2423,7 @@
     <tableColumn id="88" xr3:uid="{E4566CF4-865A-41F2-81FB-84316C489401}" name="Answer 22">
       <calculatedColumnFormula>MOD(CH2+CH1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="89" xr3:uid="{CE73AAAF-6F2F-49E7-86CB-7A222B123759}" name="Label 22" dataDxfId="62">
+    <tableColumn id="89" xr3:uid="{CE73AAAF-6F2F-49E7-86CB-7A222B123759}" name="Label 22" dataDxfId="18">
       <calculatedColumnFormula>IF(CI2=CJ2,TRUE,IF(CJ2="SKIPPED","SKIPPED",IF(CJ2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="90" xr3:uid="{3DDFB617-498D-4D70-8171-55C832443F70}" name="Soal 23"/>
@@ -2475,7 +2433,7 @@
     <tableColumn id="92" xr3:uid="{B89499B1-FA69-4A5C-82F8-12E01B28CC16}" name="Answer 23">
       <calculatedColumnFormula>MOD(CL2+CL1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="93" xr3:uid="{26F1D261-A7F9-44AB-8C9F-0F8A32F8EB00}" name="Label 23" dataDxfId="61">
+    <tableColumn id="93" xr3:uid="{26F1D261-A7F9-44AB-8C9F-0F8A32F8EB00}" name="Label 23" dataDxfId="17">
       <calculatedColumnFormula>IF(CM2=CN2,TRUE,IF(CN2="SKIPPED","SKIPPED",IF(CN2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="94" xr3:uid="{CD76AAC2-6A82-45A3-BC3F-662FEFAEB499}" name="Soal 24"/>
@@ -2485,7 +2443,7 @@
     <tableColumn id="96" xr3:uid="{5806E24B-24A7-4401-8DC4-89E9F886FB29}" name="Answer 24">
       <calculatedColumnFormula>MOD(CP2+CP1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="97" xr3:uid="{75B007C9-4223-4BF5-AD0B-915B6A7A89B5}" name="Label 24" dataDxfId="60">
+    <tableColumn id="97" xr3:uid="{75B007C9-4223-4BF5-AD0B-915B6A7A89B5}" name="Label 24" dataDxfId="16">
       <calculatedColumnFormula>IF(CQ2=CR2,TRUE,IF(CR2="SKIPPED","SKIPPED",IF(CR2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="98" xr3:uid="{4DF1955E-179F-4923-9ECC-82A5B2ECD68C}" name="Soal 25"/>
@@ -2495,7 +2453,7 @@
     <tableColumn id="100" xr3:uid="{2A2DEC00-0776-4F60-B080-7F9D1365C4E0}" name="Answer 25">
       <calculatedColumnFormula>MOD(CT2+CT1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="101" xr3:uid="{A366F81F-D588-49CA-B743-DBF635E41E89}" name="Label 25" dataDxfId="59">
+    <tableColumn id="101" xr3:uid="{A366F81F-D588-49CA-B743-DBF635E41E89}" name="Label 25" dataDxfId="15">
       <calculatedColumnFormula>IF(CU2=CV2,TRUE,IF(CV2="SKIPPED","SKIPPED",IF(CV2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="102" xr3:uid="{F02F5665-DF2F-4A51-BBF0-85D8503ACEAB}" name="Soal 26"/>
@@ -2505,7 +2463,7 @@
     <tableColumn id="104" xr3:uid="{39735D5F-CBE6-4F08-B67D-508AC5FB229D}" name="Answer 26">
       <calculatedColumnFormula>MOD(CX2+CX1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="105" xr3:uid="{E3A2DF76-A0F1-462E-BBE7-37216295AD1B}" name="Label 26" dataDxfId="58">
+    <tableColumn id="105" xr3:uid="{E3A2DF76-A0F1-462E-BBE7-37216295AD1B}" name="Label 26" dataDxfId="14">
       <calculatedColumnFormula>IF(CY2=CZ2,TRUE,IF(CZ2="SKIPPED","SKIPPED",IF(CZ2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="106" xr3:uid="{63ABB465-AC2D-4A37-855F-33BAEC454FC1}" name="Soal 27"/>
@@ -2515,7 +2473,7 @@
     <tableColumn id="108" xr3:uid="{A22D7BC7-9A88-4A77-A987-F57162397C0E}" name="Answer 27">
       <calculatedColumnFormula>MOD(DB2+DB1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="109" xr3:uid="{6A8E403C-DADA-48F9-B43F-390983CA2AEA}" name="Label 27" dataDxfId="57">
+    <tableColumn id="109" xr3:uid="{6A8E403C-DADA-48F9-B43F-390983CA2AEA}" name="Label 27" dataDxfId="13">
       <calculatedColumnFormula>IF(DC2=DD2,TRUE,IF(DD2="SKIPPED","SKIPPED",IF(DD2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="110" xr3:uid="{52DBE93F-F71B-415C-9B2F-D8DAFC145107}" name="Soal 28"/>
@@ -2525,7 +2483,7 @@
     <tableColumn id="112" xr3:uid="{24BE988D-A635-42B7-ADCF-044C0235303F}" name="Answer 28">
       <calculatedColumnFormula>MOD(DF2+DF1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="113" xr3:uid="{028C094F-2975-430D-90FC-978FC86F65D6}" name="Label 28" dataDxfId="56">
+    <tableColumn id="113" xr3:uid="{028C094F-2975-430D-90FC-978FC86F65D6}" name="Label 28" dataDxfId="12">
       <calculatedColumnFormula>IF(DG2=DH2,TRUE,IF(DH2="SKIPPED","SKIPPED",IF(DH2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="114" xr3:uid="{95420346-E882-4F45-8175-ABD3485849BC}" name="Soal 29"/>
@@ -2535,7 +2493,7 @@
     <tableColumn id="116" xr3:uid="{4C5E09BA-EE1C-4EFE-BC87-3B91A5EE49B8}" name="Answer 29">
       <calculatedColumnFormula>MOD(DJ2+DJ1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="117" xr3:uid="{A1BBE231-9D24-42DA-BB33-3B9927EDDEEF}" name="Label 29" dataDxfId="55">
+    <tableColumn id="117" xr3:uid="{A1BBE231-9D24-42DA-BB33-3B9927EDDEEF}" name="Label 29" dataDxfId="11">
       <calculatedColumnFormula>IF(DK2=DL2,TRUE,IF(DL2="SKIPPED","SKIPPED",IF(DL2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="118" xr3:uid="{F0DBBF11-69C1-48CA-82AD-7EBA837F0317}" name="Soal 30"/>
@@ -2545,7 +2503,7 @@
     <tableColumn id="120" xr3:uid="{80124F1E-1E18-4942-9D12-4EEA9EE54846}" name="Answer 30">
       <calculatedColumnFormula>MOD(DN2+DN1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="121" xr3:uid="{EE5EDBDD-F380-4623-BF50-C4DF0C55EF0B}" name="Label 30" dataDxfId="54">
+    <tableColumn id="121" xr3:uid="{EE5EDBDD-F380-4623-BF50-C4DF0C55EF0B}" name="Label 30" dataDxfId="10">
       <calculatedColumnFormula>IF(DO2=DP2,TRUE,IF(DP2="SKIPPED","SKIPPED",IF(DP2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="122" xr3:uid="{BE830144-B305-46D4-8B0D-142AFA06564C}" name="Soal 31"/>
@@ -2555,7 +2513,7 @@
     <tableColumn id="124" xr3:uid="{1F69B9A7-4594-4A76-9452-3E0235BA48FA}" name="Answer 31">
       <calculatedColumnFormula>MOD(DR2+DR1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="125" xr3:uid="{0A58380C-C715-4ACE-9B64-2A4B8CEC73FD}" name="Label 31" dataDxfId="53">
+    <tableColumn id="125" xr3:uid="{0A58380C-C715-4ACE-9B64-2A4B8CEC73FD}" name="Label 31" dataDxfId="9">
       <calculatedColumnFormula>IF(DS2=DT2,TRUE,IF(DT2="SKIPPED","SKIPPED",IF(DT2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="126" xr3:uid="{B86A2051-E1C9-460F-9B99-79D304D9AD74}" name="Soal 32"/>
@@ -2565,7 +2523,7 @@
     <tableColumn id="128" xr3:uid="{5654E9AD-440E-4236-A63D-1845908CF732}" name="Answer 32">
       <calculatedColumnFormula>MOD(DV2+DV1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="129" xr3:uid="{4855ABE1-BE0F-469C-85BE-9B2F2FB66726}" name="Label 32" dataDxfId="52">
+    <tableColumn id="129" xr3:uid="{4855ABE1-BE0F-469C-85BE-9B2F2FB66726}" name="Label 32" dataDxfId="8">
       <calculatedColumnFormula>IF(DW2=DX2,TRUE,IF(DX2="SKIPPED","SKIPPED",IF(DX2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="130" xr3:uid="{8D8EA34C-139C-44DA-B85E-8051356A600B}" name="Soal 33"/>
@@ -2575,7 +2533,7 @@
     <tableColumn id="132" xr3:uid="{D2550378-8419-46F4-85E3-B94FD5013D31}" name="Answer 33">
       <calculatedColumnFormula>MOD(DZ2+DZ1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="133" xr3:uid="{19C68391-20FE-475F-BD62-85BE8CE87F1C}" name="Label 33" dataDxfId="51">
+    <tableColumn id="133" xr3:uid="{19C68391-20FE-475F-BD62-85BE8CE87F1C}" name="Label 33" dataDxfId="7">
       <calculatedColumnFormula>IF(EA2=EB2,TRUE,IF(EB2="SKIPPED","SKIPPED",IF(EB2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="134" xr3:uid="{2E6F5C41-42FB-4620-8C7C-4BB9A18109E2}" name="Soal 34"/>
@@ -2585,7 +2543,7 @@
     <tableColumn id="136" xr3:uid="{3AD7308F-C1AC-4E56-B9F2-6B747B1C43EF}" name="Answer 34">
       <calculatedColumnFormula>MOD(ED2+ED1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="137" xr3:uid="{F5919A7E-F675-4D28-92C8-7A901137B265}" name="Label 34" dataDxfId="50">
+    <tableColumn id="137" xr3:uid="{F5919A7E-F675-4D28-92C8-7A901137B265}" name="Label 34" dataDxfId="6">
       <calculatedColumnFormula>IF(EE2=EF2,TRUE,IF(EF2="SKIPPED","SKIPPED",IF(EF2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="138" xr3:uid="{2CC69AEF-5DA6-478F-BB8B-73907B4619CE}" name="Soal 35"/>
@@ -2595,7 +2553,7 @@
     <tableColumn id="140" xr3:uid="{1CABE24B-4CA9-4580-85C5-ABC207A2BD54}" name="Answer 35">
       <calculatedColumnFormula>MOD(EH2+EH1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="141" xr3:uid="{EE6F7B4D-390C-4502-9560-58C098482018}" name="Label 35" dataDxfId="49">
+    <tableColumn id="141" xr3:uid="{EE6F7B4D-390C-4502-9560-58C098482018}" name="Label 35" dataDxfId="5">
       <calculatedColumnFormula>IF(EI2=EJ2,TRUE,IF(EJ2="SKIPPED","SKIPPED",IF(EJ2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="142" xr3:uid="{0E347977-F76E-4626-BB3B-7DF7E9C09B63}" name="Soal 36"/>
@@ -2605,7 +2563,7 @@
     <tableColumn id="144" xr3:uid="{D3640209-8ADF-480E-9FDA-48C96081D50B}" name="Answer 36">
       <calculatedColumnFormula>MOD(EL2+EL1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="145" xr3:uid="{4B919479-4195-44C3-9EB3-3B35216A1081}" name="Label 36" dataDxfId="48">
+    <tableColumn id="145" xr3:uid="{4B919479-4195-44C3-9EB3-3B35216A1081}" name="Label 36" dataDxfId="4">
       <calculatedColumnFormula>IF(EM2=EN2,TRUE,IF(EN2="SKIPPED","SKIPPED",IF(EN2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="146" xr3:uid="{D5837514-6041-4D93-AFB2-7FF4C845994B}" name="Soal 37"/>
@@ -2615,7 +2573,7 @@
     <tableColumn id="148" xr3:uid="{FC5555CF-7F7B-4FC0-B6D1-229857A5808B}" name="Answer 37">
       <calculatedColumnFormula>MOD(EP2+EP1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="149" xr3:uid="{6B431154-EFC3-4595-8EC3-0A24769CCC45}" name="Label 37" dataDxfId="47">
+    <tableColumn id="149" xr3:uid="{6B431154-EFC3-4595-8EC3-0A24769CCC45}" name="Label 37" dataDxfId="3">
       <calculatedColumnFormula>IF(EQ2=ER2,TRUE,IF(ER2="SKIPPED","SKIPPED",IF(ER2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="150" xr3:uid="{276F6CD6-3AE7-4722-A187-23A0CC61669B}" name="Soal 38"/>
@@ -2625,7 +2583,7 @@
     <tableColumn id="152" xr3:uid="{98E4E9D1-AE8E-4940-997E-83A91895AD84}" name="Answer 38">
       <calculatedColumnFormula>MOD(ET2+ET1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="153" xr3:uid="{C75BE1E7-28BE-4CBB-8ECD-9EC6E47D6148}" name="Label 38" dataDxfId="46">
+    <tableColumn id="153" xr3:uid="{C75BE1E7-28BE-4CBB-8ECD-9EC6E47D6148}" name="Label 38" dataDxfId="2">
       <calculatedColumnFormula>IF(EU2=EV2,TRUE,IF(EV2="SKIPPED","SKIPPED",IF(EV2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="154" xr3:uid="{6E7D1ABE-11DF-4060-B392-254E8AEAD8FE}" name="Soal 39"/>
@@ -2635,7 +2593,7 @@
     <tableColumn id="156" xr3:uid="{86C5A5A0-E854-41FE-A287-E650BF041434}" name="Answer 39">
       <calculatedColumnFormula>MOD(EX2+EX1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="157" xr3:uid="{6E8E5BE3-5CF2-4D56-9F33-390042E9892F}" name="Label 39" dataDxfId="45">
+    <tableColumn id="157" xr3:uid="{6E8E5BE3-5CF2-4D56-9F33-390042E9892F}" name="Label 39" dataDxfId="1">
       <calculatedColumnFormula>IF(EY2=EZ2,TRUE,IF(EZ2="SKIPPED","SKIPPED",IF(EZ2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="158" xr3:uid="{293352B7-0463-44E2-BE08-541C87599105}" name="Soal 40"/>
@@ -2645,7 +2603,7 @@
     <tableColumn id="160" xr3:uid="{AB543C10-5E3D-453E-BDE4-437F28F53523}" name="Answer 40">
       <calculatedColumnFormula>MOD(FB2+FB1,10)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="161" xr3:uid="{A8FEC182-524F-42A1-BA3C-DE9CA42E8B90}" name="Label 40" dataDxfId="44">
+    <tableColumn id="161" xr3:uid="{A8FEC182-524F-42A1-BA3C-DE9CA42E8B90}" name="Label 40" dataDxfId="0">
       <calculatedColumnFormula>IF(FC2=FD2,TRUE,IF(FD2="SKIPPED","SKIPPED",IF(FD2="N/A","BLANK",FALSE)))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -21930,7 +21888,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E46497C0-9712-468A-A7E4-A42557771246}">
-  <dimension ref="A1:FY69"/>
+  <dimension ref="A1:FE69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" customWidth="1"/>
@@ -49374,7 +49332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:181" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:161" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>9</v>
       </c>
@@ -49976,7 +49934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:181" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:161" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>8</v>
       </c>
@@ -50581,7 +50539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:181" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:161" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>7</v>
       </c>
@@ -51186,7 +51144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:181" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:161" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>6</v>
       </c>
@@ -51791,7 +51749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:181" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:161" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>5</v>
       </c>
@@ -52393,7 +52351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:181" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:161" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>4</v>
       </c>
@@ -52996,7 +52954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:181" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:161" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>3</v>
       </c>
@@ -53601,7 +53559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:181" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:161" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2</v>
       </c>
@@ -54206,7 +54164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:181" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:161" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>1</v>
       </c>
@@ -54811,7 +54769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:181" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:161" x14ac:dyDescent="0.25">
       <c r="D59" s="2" t="b">
         <v>1</v>
       </c>
@@ -54975,28 +54933,8 @@
         <f>COUNTIF(FE$2:FE$57,$D59)</f>
         <v>24</v>
       </c>
-      <c r="FI59" t="e">
-        <f>COUNTIF(#REF!,$D59)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FM59" t="e">
-        <f>COUNTIF(#REF!,$D59)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FQ59" t="e">
-        <f>COUNTIF(#REF!,$D59)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FU59" t="e">
-        <f>COUNTIF(#REF!,$D59)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FY59" t="e">
-        <f>COUNTIF(#REF!,$D59)</f>
-        <v>#REF!</v>
-      </c>
     </row>
-    <row r="60" spans="1:181" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:161" x14ac:dyDescent="0.25">
       <c r="D60" s="2" t="b">
         <v>0</v>
       </c>
@@ -55160,28 +55098,8 @@
         <f>COUNTIF(FE$2:FE$57,$D60)</f>
         <v>0</v>
       </c>
-      <c r="FI60" t="e">
-        <f>COUNTIF(#REF!,$D60)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FM60" t="e">
-        <f>COUNTIF(#REF!,$D60)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FQ60" t="e">
-        <f>COUNTIF(#REF!,$D60)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FU60" t="e">
-        <f>COUNTIF(#REF!,$D60)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FY60" t="e">
-        <f>COUNTIF(#REF!,$D60)</f>
-        <v>#REF!</v>
-      </c>
     </row>
-    <row r="61" spans="1:181" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:161" x14ac:dyDescent="0.25">
       <c r="D61" s="2" t="s">
         <v>2</v>
       </c>
@@ -55345,28 +55263,8 @@
         <f>COUNTIF(FE$2:FE$57,$D61)</f>
         <v>0</v>
       </c>
-      <c r="FI61" t="e">
-        <f>COUNTIF(#REF!,$D61)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FM61" t="e">
-        <f>COUNTIF(#REF!,$D61)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FQ61" t="e">
-        <f>COUNTIF(#REF!,$D61)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FU61" t="e">
-        <f>COUNTIF(#REF!,$D61)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FY61" t="e">
-        <f>COUNTIF(#REF!,$D61)</f>
-        <v>#REF!</v>
-      </c>
     </row>
-    <row r="62" spans="1:181" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:161" x14ac:dyDescent="0.25">
       <c r="D62" s="2" t="s">
         <v>3</v>
       </c>
@@ -55530,28 +55428,8 @@
         <f>COUNTIF(FE$2:FE$57,$D62)</f>
         <v>31</v>
       </c>
-      <c r="FI62" t="e">
-        <f>COUNTIF(#REF!,$D62)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FM62" t="e">
-        <f>COUNTIF(#REF!,$D62)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FQ62" t="e">
-        <f>COUNTIF(#REF!,$D62)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FU62" t="e">
-        <f>COUNTIF(#REF!,$D62)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="FY62" t="e">
-        <f>COUNTIF(#REF!,$D62)</f>
-        <v>#REF!</v>
-      </c>
     </row>
-    <row r="63" spans="1:181" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:161" x14ac:dyDescent="0.25">
       <c r="D63" t="s">
         <v>1</v>
       </c>
@@ -55578,192 +55456,192 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E2:E57 I2:I57 M2:M57 Q3:Q57 U3:U57 Y3:Y57 AC3:AC57 AG3:AG57 AK3:AK57 AO3:AO57 AS3:AS57 AW3:AW57 BA3:BA57 BE3:BE57 BI3:BI57 BM3:BM57 BQ3:BQ57 BU3:BU57 BY3:BY57 CC3:CC57 CG3:CG57 CK3:CK57 CO3:CO57 CS3:CS57 CW3:CW57 DA3:DA57 DE3:DE57 DI3:DI57 DM3:DM57 DQ3:DQ57 DU3:DU57 DY3:DY57 EC3:EC57 EG3:EG57 EK3:EK57 EO3:EO57 ES3:ES57 EW3:EW57 FA3:FA57 FE3:FE57">
-    <cfRule type="expression" dxfId="43" priority="88">
+    <cfRule type="expression" dxfId="78" priority="88">
       <formula>C2=D2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2">
-    <cfRule type="expression" dxfId="42" priority="42">
+    <cfRule type="expression" dxfId="77" priority="42">
       <formula>O2=P2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2">
-    <cfRule type="expression" dxfId="41" priority="41">
+    <cfRule type="expression" dxfId="76" priority="41">
       <formula>S2=T2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2">
-    <cfRule type="expression" dxfId="40" priority="40">
+    <cfRule type="expression" dxfId="75" priority="40">
       <formula>W2=X2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC2">
-    <cfRule type="expression" dxfId="39" priority="39">
+    <cfRule type="expression" dxfId="74" priority="39">
       <formula>AA2=AB2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG2">
-    <cfRule type="expression" dxfId="38" priority="38">
+    <cfRule type="expression" dxfId="73" priority="38">
       <formula>AE2=AF2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2">
-    <cfRule type="expression" dxfId="37" priority="37">
+    <cfRule type="expression" dxfId="72" priority="37">
       <formula>AI2=AJ2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AO2">
-    <cfRule type="expression" dxfId="36" priority="36">
+    <cfRule type="expression" dxfId="71" priority="36">
       <formula>AM2=AN2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AS2">
-    <cfRule type="expression" dxfId="35" priority="35">
+    <cfRule type="expression" dxfId="70" priority="35">
       <formula>AQ2=AR2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AW2">
-    <cfRule type="expression" dxfId="34" priority="34">
+    <cfRule type="expression" dxfId="69" priority="34">
       <formula>AU2=AV2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA2">
-    <cfRule type="expression" dxfId="33" priority="33">
+    <cfRule type="expression" dxfId="68" priority="33">
       <formula>AY2=AZ2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BE2">
-    <cfRule type="expression" dxfId="32" priority="32">
+    <cfRule type="expression" dxfId="67" priority="32">
       <formula>BC2=BD2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI2">
-    <cfRule type="expression" dxfId="31" priority="31">
+    <cfRule type="expression" dxfId="66" priority="31">
       <formula>BG2=BH2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM2">
-    <cfRule type="expression" dxfId="30" priority="30">
+    <cfRule type="expression" dxfId="65" priority="30">
       <formula>BK2=BL2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BQ2">
-    <cfRule type="expression" dxfId="29" priority="29">
+    <cfRule type="expression" dxfId="64" priority="29">
       <formula>BO2=BP2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BU2">
-    <cfRule type="expression" dxfId="28" priority="28">
+    <cfRule type="expression" dxfId="63" priority="28">
       <formula>BS2=BT2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BY2">
-    <cfRule type="expression" dxfId="27" priority="27">
+    <cfRule type="expression" dxfId="62" priority="27">
       <formula>BW2=BX2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CC2">
-    <cfRule type="expression" dxfId="26" priority="26">
+    <cfRule type="expression" dxfId="61" priority="26">
       <formula>CA2=CB2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CG2">
-    <cfRule type="expression" dxfId="25" priority="25">
+    <cfRule type="expression" dxfId="60" priority="25">
       <formula>CE2=CF2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CK2">
-    <cfRule type="expression" dxfId="23" priority="24">
+    <cfRule type="expression" dxfId="59" priority="24">
       <formula>CI2=CJ2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CO2">
-    <cfRule type="expression" dxfId="22" priority="23">
+    <cfRule type="expression" dxfId="58" priority="23">
       <formula>CM2=CN2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CS2">
-    <cfRule type="expression" dxfId="21" priority="22">
+    <cfRule type="expression" dxfId="57" priority="22">
       <formula>CQ2=CR2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="CW2">
-    <cfRule type="expression" dxfId="20" priority="21">
+    <cfRule type="expression" dxfId="56" priority="21">
       <formula>CU2=CV2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DA2">
-    <cfRule type="expression" dxfId="19" priority="20">
+    <cfRule type="expression" dxfId="55" priority="20">
       <formula>CY2=CZ2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DE2">
-    <cfRule type="expression" dxfId="18" priority="19">
+    <cfRule type="expression" dxfId="54" priority="19">
       <formula>DC2=DD2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DI2">
-    <cfRule type="expression" dxfId="17" priority="18">
+    <cfRule type="expression" dxfId="53" priority="18">
       <formula>DG2=DH2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DM2">
-    <cfRule type="expression" dxfId="16" priority="17">
+    <cfRule type="expression" dxfId="52" priority="17">
       <formula>DK2=DL2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DQ2">
-    <cfRule type="expression" dxfId="15" priority="16">
+    <cfRule type="expression" dxfId="51" priority="16">
       <formula>DO2=DP2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DU2">
-    <cfRule type="expression" dxfId="14" priority="15">
+    <cfRule type="expression" dxfId="50" priority="15">
       <formula>DS2=DT2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="DY2">
-    <cfRule type="expression" dxfId="13" priority="14">
+    <cfRule type="expression" dxfId="49" priority="14">
       <formula>DW2=DX2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EC2">
-    <cfRule type="expression" dxfId="12" priority="13">
+    <cfRule type="expression" dxfId="48" priority="13">
       <formula>EA2=EB2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EG2">
-    <cfRule type="expression" dxfId="11" priority="12">
+    <cfRule type="expression" dxfId="47" priority="12">
       <formula>EE2=EF2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EK2">
-    <cfRule type="expression" dxfId="10" priority="11">
+    <cfRule type="expression" dxfId="46" priority="11">
       <formula>EI2=EJ2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EO2">
-    <cfRule type="expression" dxfId="9" priority="10">
+    <cfRule type="expression" dxfId="45" priority="10">
       <formula>EM2=EN2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="ES2">
-    <cfRule type="expression" dxfId="8" priority="9">
+    <cfRule type="expression" dxfId="44" priority="9">
       <formula>EQ2=ER2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="EW2">
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="43" priority="8">
       <formula>EU2=EV2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FA2">
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" dxfId="42" priority="7">
       <formula>EY2=EZ2</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="FE2">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="41" priority="6">
       <formula>FC2=FD2</formula>
     </cfRule>
   </conditionalFormatting>
